--- a/examples/sample_after.xlsx
+++ b/examples/sample_after.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -515,9 +515,35 @@
         <v>22525</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Cohorts</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Revenue per cohort</v>
+      </c>
+      <c r="B14" t="e">
+        <f>B9/B13</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Prior year revenue</v>
+      </c>
+      <c r="B16" t="e">
+        <f>#REF!B9</f>
+        <v>#REF!</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/examples/sample_after.xlsx
+++ b/examples/sample_after.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -541,9 +541,41 @@
         <v>#REF!</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Monthly ramp</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19">
+        <f>B18*1.01</f>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20">
+        <f>B19*1.05</f>
+        <v>106.05</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21">
+        <f>B20*1.01</f>
+        <v>107.1105</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22">
+        <f>B21*1.01</f>
+        <v>108.181605</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/examples/sample_after.xlsx
+++ b/examples/sample_after.xlsx
@@ -582,7 +582,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -594,15 +594,18 @@
         <v>Item</v>
       </c>
       <c r="B3" t="str">
+        <v>FY prior</v>
+      </c>
+      <c r="C3" t="str">
         <v>Q1</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>Q2</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>Q3</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Q4</v>
       </c>
     </row>
@@ -611,15 +614,18 @@
         <v>Salaries</v>
       </c>
       <c r="B4">
+        <v>400</v>
+      </c>
+      <c r="C4">
         <v>420</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>430</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>440</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>450</v>
       </c>
     </row>
@@ -628,15 +634,18 @@
         <v>Rent</v>
       </c>
       <c r="B5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C5">
         <v>90</v>
       </c>
       <c r="D5">
+        <v>90</v>
+      </c>
+      <c r="E5">
         <v>95</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>95</v>
       </c>
     </row>
@@ -645,15 +654,18 @@
         <v>Travel</v>
       </c>
       <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
         <v>12</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>14</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>11</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>16</v>
       </c>
     </row>
@@ -662,15 +674,18 @@
         <v>Software</v>
       </c>
       <c r="B7">
+        <v>55</v>
+      </c>
+      <c r="C7">
         <v>60</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>62</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>64</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>66</v>
       </c>
     </row>
@@ -680,24 +695,28 @@
       </c>
       <c r="B8">
         <f>SUM(B4:B7)</f>
-        <v>582</v>
+        <v>549</v>
       </c>
       <c r="C8">
         <f>SUM(C4:C7)</f>
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="D8">
         <f>SUM(D4:D7)</f>
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="E8">
         <f>SUM(E4:E7)</f>
+        <v>610</v>
+      </c>
+      <c r="F8">
+        <f>SUM(F4:F7)</f>
         <v>627</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/examples/sample_after.xlsx
+++ b/examples/sample_after.xlsx
@@ -7,6 +7,11 @@
     <sheet name="Operating costs" sheetId="2" r:id="rId2"/>
     <sheet name="Sensitivity" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="GrowthRate">'Revenue build'!$B$13</definedName>
+    <definedName name="TAX1">'Revenue build'!$B$24</definedName>
+    <definedName name="Headroom">'Sensitivity'!$B$5</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -399,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -573,16 +578,24 @@
         <v>108.181605</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Tax rate</v>
+      </c>
+      <c r="B24">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -714,9 +727,30 @@
         <v>627</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>After tax</v>
+      </c>
+      <c r="C9">
+        <f>C8*TAX1</f>
+        <v>116.4</v>
+      </c>
+      <c r="D9">
+        <f>D8*TAX1</f>
+        <v>119.2</v>
+      </c>
+      <c r="E9">
+        <f>E8*TAX1</f>
+        <v>122</v>
+      </c>
+      <c r="F9">
+        <f>F8*TAX1</f>
+        <v>125.4</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
   </ignoredErrors>
 </worksheet>
 </file>
